--- a/ZCloud-市政财务-002-20261022/muskegon-acceleration-clause/targets/answer.xlsx
+++ b/ZCloud-市政财务-002-20261022/muskegon-acceleration-clause/targets/answer.xlsx
@@ -47,8 +47,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,13 +427,13 @@
   <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
-    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="108" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="26" customHeight="1">
       <c r="A1" t="inlineStr">
         <is>
           <t>label</t>
@@ -445,61 +455,61 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="2" ht="115" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Plan A principal balance</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" s="4" t="n">
         <v>42200</v>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Agreement.pdf, PDF p.5 sections 3C-3D: earned term-revenue commission and normal payment timing; PDF p.7 section 4F: early termination accelerates the entire unpaid base fees, commissions and expenses. Records.pdf, PDF p.2 Plans, Plan A: termination 2007-12-31, no amendments or other principal. PDF p.3 Sponsorships, records A1 and A2: term cash USD 235,000 and 347,000, accepted 2007-05-01, first revenue 2007-06-01, no escalations/in-kind/benefits; 10% earned commission USD 58,200. PDF p.4 Broker payments, Plan A, 2007-07-15 USD 9,200 and 2007-08-15 USD 6,800. Agreement.pdf, PDF p.4 section 3A, and Records.pdf, PDF p.5 Other payments: base fee fully paid, expenses zero. Detail record A date comes from Plans; value and this principal balance are USD 42,200 = 58,200 - 9,200 - 6,800.</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="3" ht="115" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Plan B principal balance</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" s="4" t="n">
         <v>55200</v>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Agreement.pdf, PDF p.5 sections 3C-3D: earned term-revenue commission and normal payment timing; PDF p.7 section 4F: early termination accelerates the entire unpaid base fees, commissions and expenses. Records.pdf, PDF p.2 Plans, Plan B: termination 2007-12-31, no amendments or other principal. PDF p.3 Sponsorships, records B1 and B2: term cash USD 318,000 and 429,000, accepted 2007-05-01, first revenue 2007-06-01, no escalations/in-kind/benefits; 10% earned commission USD 74,700. PDF p.4 Broker payments, Plan B, 2007-07-15 USD 11,200 and 2007-08-15 USD 8,300. Agreement.pdf, PDF p.4 section 3A, and Records.pdf, PDF p.5 Other payments: base fee fully paid, expenses zero. Detail record B date comes from Plans; value and this principal balance are USD 55,200 = 74,700 - 11,200 - 8,300.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="4" ht="115" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Plan C principal balance</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" s="4" t="n">
         <v>50500</v>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Agreement.pdf, PDF p.5 sections 3C-3D: earned term-revenue commission and normal payment timing; PDF p.7 section 4F: early termination accelerates the entire unpaid base fees, commissions and expenses. Records.pdf, PDF p.2 Plans, Plan C: termination 2007-12-31, no amendments or other principal. PDF p.3 Sponsorships, records C1 and C2: term cash USD 287,000 and 386,000, accepted 2007-05-01, first revenue 2007-06-01, no escalations/in-kind/benefits; 10% earned commission USD 67,300. PDF p.4 Broker payments, Plan C, 2007-07-15 USD 9,700 and 2007-08-15 USD 7,100. Agreement.pdf, PDF p.4 section 3A, and Records.pdf, PDF p.5 Other payments: base fee fully paid, expenses zero. Detail record C date comes from Plans; value and this principal balance are USD 50,500 = 67,300 - 9,700 - 7,100.</t>
         </is>
@@ -552,7 +562,7 @@
           <t>2007-12-31</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="1" t="n">
         <v>42200</v>
       </c>
     </row>
@@ -567,7 +577,7 @@
           <t>2007-12-31</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" s="1" t="n">
         <v>55200</v>
       </c>
     </row>
@@ -582,7 +592,7 @@
           <t>2007-12-31</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" s="1" t="n">
         <v>50500</v>
       </c>
     </row>
